--- a/data/trans_orig/P36BPD07_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD07_R-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>256927</t>
+          <t>258008</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>298145</t>
+          <t>296497</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>275901</t>
+          <t>274163</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>310326</t>
+          <t>307326</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>543164</t>
+          <t>542858</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>595345</t>
+          <t>594923</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,17%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>119165</t>
+          <t>120813</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>160383</t>
+          <t>159302</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85429</t>
+          <t>88429</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>119854</t>
+          <t>121592</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>217720</t>
+          <t>218142</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>269901</t>
+          <t>270207</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>427755</t>
+          <t>423817</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>467920</t>
+          <t>465783</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>414991</t>
+          <t>415416</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>454211</t>
+          <t>454014</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>855458</t>
+          <t>854875</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>910042</t>
+          <t>910471</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,03%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>121530</t>
+          <t>123667</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>161695</t>
+          <t>165633</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>108356</t>
+          <t>108553</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>147576</t>
+          <t>147151</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>241975</t>
+          <t>241546</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>296559</t>
+          <t>297142</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,79%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>531846</t>
+          <t>533747</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>573504</t>
+          <t>570118</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>516331</t>
+          <t>516807</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>555728</t>
+          <t>555406</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1062915</t>
+          <t>1061406</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1116768</t>
+          <t>1116303</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,21%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93518</t>
+          <t>96904</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>133275</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>102919</t>
+          <t>103241</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>142316</t>
+          <t>141840</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>208901</t>
+          <t>209366</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>262754</t>
+          <t>264263</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>531408</t>
+          <t>532756</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>567929</t>
+          <t>568779</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>557963</t>
+          <t>557667</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>590136</t>
+          <t>589273</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1102525</t>
+          <t>1099280</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1152352</t>
+          <t>1150401</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,18%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>77197</t>
+          <t>76347</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>113718</t>
+          <t>112370</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54662</t>
+          <t>55525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86835</t>
+          <t>87131</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>137572</t>
+          <t>139523</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>187399</t>
+          <t>190644</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>439034</t>
+          <t>438512</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>458538</t>
+          <t>458259</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>453668</t>
+          <t>453438</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>476675</t>
+          <t>475939</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>901583</t>
+          <t>899798</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>930986</t>
+          <t>931134</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11590</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30815</t>
+          <t>31337</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17761</t>
+          <t>18497</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40768</t>
+          <t>40998</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33299</t>
+          <t>33151</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>62702</t>
+          <t>64487</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>314196</t>
+          <t>313953</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>327157</t>
+          <t>326587</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>361063</t>
+          <t>360880</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>372540</t>
+          <t>372536</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>679480</t>
+          <t>678810</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>697112</t>
+          <t>696716</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>18258</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15593</t>
+          <t>15776</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11755</t>
+          <t>12151</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>29387</t>
+          <t>30057</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>235036</t>
+          <t>235726</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>246185</t>
+          <t>246586</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>368286</t>
+          <t>368058</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>383467</t>
+          <t>383214</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>609325</t>
+          <t>609190</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>627651</t>
+          <t>627995</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15102</t>
+          <t>14412</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21122</t>
+          <t>21350</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>11895</t>
+          <t>11551</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>30221</t>
+          <t>30356</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2800989</t>
+          <t>2803345</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2889160</t>
+          <t>2886551</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3014471</t>
+          <t>3014342</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3093012</t>
+          <t>3093238</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5843895</t>
+          <t>5838447</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5960210</t>
+          <t>5961622</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,48%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>481946</t>
+          <t>484555</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>570117</t>
+          <t>567761</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>429255</t>
+          <t>429029</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>507796</t>
+          <t>507925</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>933163</t>
+          <t>931751</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1049478</t>
+          <t>1054926</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -3705,32 +3705,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>267552</t>
+          <t>263464</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>233376</t>
+          <t>234903</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>298542</t>
+          <t>291776</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3740,32 +3740,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>202181</t>
+          <t>226144</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>177161</t>
+          <t>200707</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>223035</t>
+          <t>250130</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3775,32 +3775,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>469732</t>
+          <t>489608</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>428618</t>
+          <t>452596</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>507983</t>
+          <t>530337</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>68,85%</t>
         </is>
       </c>
     </row>
@@ -3818,32 +3818,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>132435</t>
+          <t>144329</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101445</t>
+          <t>116017</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>166611</t>
+          <t>172890</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3853,32 +3853,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>111019</t>
+          <t>136368</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90165</t>
+          <t>112382</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136039</t>
+          <t>161805</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3888,32 +3888,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>243455</t>
+          <t>280697</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>205204</t>
+          <t>239968</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>284569</t>
+          <t>317709</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -3931,17 +3931,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3966,17 +3966,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4001,17 +4001,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4048,32 +4048,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>266454</t>
+          <t>306363</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>238200</t>
+          <t>279149</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>291061</t>
+          <t>332208</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4083,32 +4083,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>399050</t>
+          <t>371245</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>374092</t>
+          <t>350878</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>445042</t>
+          <t>391357</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4118,32 +4118,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>665504</t>
+          <t>677608</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>626218</t>
+          <t>642775</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>733902</t>
+          <t>710784</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>72,75%</t>
         </is>
       </c>
     </row>
@@ -4161,32 +4161,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>157093</t>
+          <t>170527</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>132486</t>
+          <t>144682</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>185347</t>
+          <t>197741</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4196,32 +4196,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>111457</t>
+          <t>128892</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>65465</t>
+          <t>108780</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>136415</t>
+          <t>149259</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4231,32 +4231,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>268550</t>
+          <t>299419</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>200152</t>
+          <t>266243</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>307836</t>
+          <t>334252</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>34,21%</t>
         </is>
       </c>
     </row>
@@ -4274,17 +4274,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4309,17 +4309,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>510507</t>
+          <t>500137</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>510507</t>
+          <t>500137</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>510507</t>
+          <t>500137</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4344,17 +4344,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>934054</t>
+          <t>977027</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>934054</t>
+          <t>977027</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>934054</t>
+          <t>977027</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4391,32 +4391,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>378423</t>
+          <t>430766</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>357789</t>
+          <t>406056</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>399866</t>
+          <t>456147</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4426,32 +4426,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>392111</t>
+          <t>448142</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>375138</t>
+          <t>428453</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>409535</t>
+          <t>466768</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4461,32 +4461,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>770534</t>
+          <t>878907</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>741351</t>
+          <t>847784</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>796421</t>
+          <t>908632</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,31%</t>
         </is>
       </c>
     </row>
@@ -4504,32 +4504,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>156819</t>
+          <t>188872</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>135376</t>
+          <t>163491</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>177453</t>
+          <t>213582</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4539,32 +4539,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>149309</t>
+          <t>171719</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131885</t>
+          <t>153093</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166282</t>
+          <t>191408</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4574,32 +4574,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>306128</t>
+          <t>360592</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>280241</t>
+          <t>330867</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>335311</t>
+          <t>391715</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -4617,17 +4617,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>535242</t>
+          <t>619638</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>535242</t>
+          <t>619638</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>535242</t>
+          <t>619638</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4652,17 +4652,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541420</t>
+          <t>619861</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541420</t>
+          <t>619861</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541420</t>
+          <t>619861</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4687,17 +4687,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1076662</t>
+          <t>1239499</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1076662</t>
+          <t>1239499</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1076662</t>
+          <t>1239499</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>703653</t>
+          <t>497066</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>622445</t>
+          <t>468892</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>813587</t>
+          <t>520109</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>554450</t>
+          <t>557281</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>535555</t>
+          <t>538510</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>582761</t>
+          <t>575050</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1258103</t>
+          <t>1054348</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1183774</t>
+          <t>1023828</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1382047</t>
+          <t>1087557</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>75,71%</t>
         </is>
       </c>
     </row>
@@ -4847,32 +4847,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>184133</t>
+          <t>203551</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>74199</t>
+          <t>180508</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>265341</t>
+          <t>231725</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4882,32 +4882,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>157367</t>
+          <t>178531</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>129056</t>
+          <t>160762</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>176262</t>
+          <t>197302</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4917,32 +4917,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>341501</t>
+          <t>382082</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>217557</t>
+          <t>348873</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>415830</t>
+          <t>412602</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -4960,17 +4960,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4995,17 +4995,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711817</t>
+          <t>735812</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>711817</t>
+          <t>735812</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>711817</t>
+          <t>735812</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5030,17 +5030,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1599604</t>
+          <t>1436430</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1599604</t>
+          <t>1436430</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1599604</t>
+          <t>1436430</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5077,32 +5077,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>418603</t>
+          <t>453479</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>398366</t>
+          <t>433044</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>436189</t>
+          <t>472891</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5112,32 +5112,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>437378</t>
+          <t>485982</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>423021</t>
+          <t>470152</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>451604</t>
+          <t>500685</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>855982</t>
+          <t>939462</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>832504</t>
+          <t>911855</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>879791</t>
+          <t>962183</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,24%</t>
         </is>
       </c>
     </row>
@@ -5190,32 +5190,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>139804</t>
+          <t>152984</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>122218</t>
+          <t>133572</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>160041</t>
+          <t>173419</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5225,32 +5225,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>109488</t>
+          <t>121768</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95262</t>
+          <t>107065</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>123845</t>
+          <t>137598</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5260,32 +5260,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>249292</t>
+          <t>274752</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>225483</t>
+          <t>252031</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>272770</t>
+          <t>302359</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -5303,17 +5303,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>558407</t>
+          <t>606463</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>558407</t>
+          <t>606463</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>558407</t>
+          <t>606463</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5338,17 +5338,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>546866</t>
+          <t>607750</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>546866</t>
+          <t>607750</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>546866</t>
+          <t>607750</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5373,17 +5373,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1105274</t>
+          <t>1214214</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1105274</t>
+          <t>1214214</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1105274</t>
+          <t>1214214</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5420,32 +5420,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>293141</t>
+          <t>324633</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>280330</t>
+          <t>309852</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>305351</t>
+          <t>337150</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>539889</t>
+          <t>363354</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>500242</t>
+          <t>351351</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>580485</t>
+          <t>374958</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>833031</t>
+          <t>687987</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>790249</t>
+          <t>668994</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>902993</t>
+          <t>703763</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>83,39%</t>
         </is>
       </c>
     </row>
@@ -5533,32 +5533,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>74105</t>
+          <t>81374</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61895</t>
+          <t>68857</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>86916</t>
+          <t>96155</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5568,32 +5568,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>67312</t>
+          <t>74552</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26716</t>
+          <t>62948</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>106959</t>
+          <t>86555</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5603,32 +5603,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>141417</t>
+          <t>155926</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>71455</t>
+          <t>140150</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>184199</t>
+          <t>174919</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -5646,17 +5646,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367246</t>
+          <t>406007</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367246</t>
+          <t>406007</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367246</t>
+          <t>406007</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5681,17 +5681,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607201</t>
+          <t>437906</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607201</t>
+          <t>437906</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607201</t>
+          <t>437906</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5716,17 +5716,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>974448</t>
+          <t>843913</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>974448</t>
+          <t>843913</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>974448</t>
+          <t>843913</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>224349</t>
+          <t>245232</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>213580</t>
+          <t>232215</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>233759</t>
+          <t>256919</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>361242</t>
+          <t>392272</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>349018</t>
+          <t>381316</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>370856</t>
+          <t>402771</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>585592</t>
+          <t>637504</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>570301</t>
+          <t>622505</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>599581</t>
+          <t>652401</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,27%</t>
         </is>
       </c>
     </row>
@@ -5876,32 +5876,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>58410</t>
+          <t>64966</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>49000</t>
+          <t>53279</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>69179</t>
+          <t>77983</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5911,32 +5911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>64041</t>
+          <t>71727</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>54427</t>
+          <t>61228</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>76265</t>
+          <t>82683</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5946,32 +5946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>122451</t>
+          <t>136693</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>108462</t>
+          <t>121796</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>137742</t>
+          <t>151692</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -5989,17 +5989,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6024,17 +6024,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425283</t>
+          <t>463999</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425283</t>
+          <t>463999</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425283</t>
+          <t>463999</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6059,17 +6059,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708043</t>
+          <t>774197</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708043</t>
+          <t>774197</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708043</t>
+          <t>774197</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2552177</t>
+          <t>2521004</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2462346</t>
+          <t>2460119</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2756369</t>
+          <t>2583832</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2886300</t>
+          <t>2844420</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2813060</t>
+          <t>2794219</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3020270</t>
+          <t>2894783</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>5438477</t>
+          <t>5365424</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5307759</t>
+          <t>5287905</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5654380</t>
+          <t>5446729</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -6219,32 +6219,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>902799</t>
+          <t>1006603</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>698607</t>
+          <t>943775</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>992630</t>
+          <t>1067488</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6254,32 +6254,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>769995</t>
+          <t>883558</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>636025</t>
+          <t>833195</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>843235</t>
+          <t>933759</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6289,32 +6289,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1672794</t>
+          <t>1890161</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1456891</t>
+          <t>1808856</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1803512</t>
+          <t>1967680</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>27,12%</t>
         </is>
       </c>
     </row>
@@ -6332,17 +6332,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3454976</t>
+          <t>3527607</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3454976</t>
+          <t>3527607</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3454976</t>
+          <t>3527607</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3656295</t>
+          <t>3727978</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3656295</t>
+          <t>3727978</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3656295</t>
+          <t>3727978</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6402,17 +6402,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7111271</t>
+          <t>7255585</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7111271</t>
+          <t>7255585</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7111271</t>
+          <t>7255585</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
